--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.00846748557122654</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31858793</v>
+        <v>4184375</v>
       </c>
       <c r="L2" t="n">
-        <v>18089246</v>
+        <v>2062274</v>
       </c>
       <c r="M2" t="n">
-        <v>4514349</v>
+        <v>448525</v>
       </c>
       <c r="N2" t="n">
-        <v>251815</v>
+        <v>14109</v>
       </c>
       <c r="O2" t="n">
-        <v>2665231</v>
+        <v>269513</v>
       </c>
       <c r="P2" t="n">
-        <v>1049234</v>
+        <v>99534</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999900460243225</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8878584504127502</v>
+        <v>0.8000978827476501</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7827607393264771</v>
+        <v>0.6299980282783508</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7292463183403015</v>
+        <v>0.5317251086235046</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3998485207557678</v>
+        <v>0.1165022104978561</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7746086716651917</v>
+        <v>0.5816354751586914</v>
       </c>
       <c r="W2" t="n">
-        <v>0.850504994392395</v>
+        <v>0.7197275161743164</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029527753233312</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>31858793</v>
+        <v>4184375</v>
       </c>
       <c r="E3" t="n">
-        <v>3451937</v>
+        <v>823925</v>
       </c>
       <c r="F3" t="n">
-        <v>77149</v>
+        <v>24872</v>
       </c>
       <c r="G3" t="n">
-        <v>8322</v>
+        <v>2247</v>
       </c>
       <c r="H3" t="n">
-        <v>4162</v>
+        <v>1556</v>
       </c>
       <c r="I3" t="n">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="J3" t="n">
-        <v>70486898</v>
+        <v>10069588</v>
       </c>
       <c r="K3" t="n">
-        <v>75487445</v>
+        <v>10333488</v>
       </c>
       <c r="L3" t="n">
-        <v>86895066</v>
+        <v>11902934</v>
       </c>
       <c r="M3" t="n">
-        <v>106692380</v>
+        <v>15083918</v>
       </c>
       <c r="N3" t="n">
-        <v>113908320</v>
+        <v>16219369</v>
       </c>
       <c r="O3" t="n">
-        <v>110569177</v>
+        <v>15711680</v>
       </c>
       <c r="P3" t="n">
-        <v>113374042</v>
+        <v>16183733</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8999504446983337</v>
+        <v>0.8307180404663086</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7866040468215942</v>
+        <v>0.6245759129524231</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6898941993713379</v>
+        <v>0.4786415994167328</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4024410247802734</v>
+        <v>0.1574050337076187</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7471264600753784</v>
+        <v>0.5279785990715027</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7751822471618652</v>
+        <v>0.514369010925293</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03201304320695698</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3794649</v>
+        <v>977363</v>
       </c>
       <c r="E4" t="n">
-        <v>18089246</v>
+        <v>2062274</v>
       </c>
       <c r="F4" t="n">
-        <v>978121</v>
+        <v>219528</v>
       </c>
       <c r="G4" t="n">
-        <v>47499</v>
+        <v>14950</v>
       </c>
       <c r="H4" t="n">
-        <v>80057</v>
+        <v>25454</v>
       </c>
       <c r="I4" t="n">
-        <v>7045</v>
+        <v>2305</v>
       </c>
       <c r="J4" t="n">
-        <v>442</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>4023947</v>
+        <v>1045454</v>
       </c>
       <c r="L4" t="n">
-        <v>5020300</v>
+        <v>1211187</v>
       </c>
       <c r="M4" t="n">
-        <v>1676082</v>
+        <v>395003</v>
       </c>
       <c r="N4" t="n">
-        <v>377961</v>
+        <v>106996</v>
       </c>
       <c r="O4" t="n">
-        <v>775514</v>
+        <v>193858</v>
       </c>
       <c r="P4" t="n">
-        <v>184426</v>
+        <v>38760</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.9999974370002747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8938635587692261</v>
+        <v>0.8151204586029053</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7846776843070984</v>
+        <v>0.6272752285003662</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7090246081352234</v>
+        <v>0.5037888884544373</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4011406004428864</v>
+        <v>0.1338995844125748</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7606194019317627</v>
+        <v>0.5535097122192383</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8110986948013306</v>
+        <v>0.5999619960784912</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>152529</v>
+        <v>48764</v>
       </c>
       <c r="E5" t="n">
-        <v>1338525</v>
+        <v>317214</v>
       </c>
       <c r="F5" t="n">
-        <v>4514349</v>
+        <v>448525</v>
       </c>
       <c r="G5" t="n">
-        <v>136327</v>
+        <v>34017</v>
       </c>
       <c r="H5" t="n">
-        <v>369984</v>
+        <v>79515</v>
       </c>
       <c r="I5" t="n">
-        <v>31815</v>
+        <v>9044</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3541815</v>
+        <v>852683</v>
       </c>
       <c r="L5" t="n">
-        <v>4907388</v>
+        <v>1239605</v>
       </c>
       <c r="M5" t="n">
-        <v>2029189</v>
+        <v>488554</v>
       </c>
       <c r="N5" t="n">
-        <v>373904</v>
+        <v>75526</v>
       </c>
       <c r="O5" t="n">
-        <v>902078</v>
+        <v>240949</v>
       </c>
       <c r="P5" t="n">
-        <v>304298</v>
+        <v>93973</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999961256980896</v>
+        <v>0.9999980330467224</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9341604113578796</v>
+        <v>0.8843727707862854</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9136061668395996</v>
+        <v>0.8507071137428284</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9677555561065674</v>
+        <v>0.946177065372467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.993457019329071</v>
+        <v>0.9888814687728882</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9854010939598083</v>
+        <v>0.9735132455825806</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9957469701766968</v>
+        <v>0.9919143915176392</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>72080</v>
+        <v>16389</v>
       </c>
       <c r="E6" t="n">
-        <v>102532</v>
+        <v>21904</v>
       </c>
       <c r="F6" t="n">
-        <v>133506</v>
+        <v>25789</v>
       </c>
       <c r="G6" t="n">
-        <v>251815</v>
+        <v>14109</v>
       </c>
       <c r="H6" t="n">
-        <v>59752</v>
+        <v>10291</v>
       </c>
       <c r="I6" t="n">
-        <v>5967</v>
+        <v>1147</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4501</v>
+        <v>2881</v>
       </c>
       <c r="E7" t="n">
-        <v>119372</v>
+        <v>44490</v>
       </c>
       <c r="F7" t="n">
-        <v>464689</v>
+        <v>116294</v>
       </c>
       <c r="G7" t="n">
-        <v>174057</v>
+        <v>51093</v>
       </c>
       <c r="H7" t="n">
-        <v>2665231</v>
+        <v>269513</v>
       </c>
       <c r="I7" t="n">
-        <v>139374</v>
+        <v>26187</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>244</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>7934</v>
+        <v>3654</v>
       </c>
       <c r="F8" t="n">
-        <v>22617</v>
+        <v>8520</v>
       </c>
       <c r="G8" t="n">
-        <v>11756</v>
+        <v>4689</v>
       </c>
       <c r="H8" t="n">
-        <v>261559</v>
+        <v>77042</v>
       </c>
       <c r="I8" t="n">
-        <v>1049234</v>
+        <v>99534</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
